--- a/docs/downloads/11/tbl_cata_type_marovoay_tous.xlsx
+++ b/docs/downloads/11/tbl_cata_type_marovoay_tous.xlsx
@@ -459,12 +459,6 @@
           <t>Autres bestioles</t>
         </is>
       </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>2.8</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -477,12 +471,6 @@
           <t>Inondation</t>
         </is>
       </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>2.8</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -495,12 +483,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -513,12 +495,6 @@
           <t>Criquets</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -531,12 +507,6 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -621,12 +591,6 @@
           <t>Autres bestioles</t>
         </is>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>3.3</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,12 +603,6 @@
           <t>Inondation</t>
         </is>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>1.6</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -657,12 +615,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -675,12 +627,6 @@
           <t>Criquets</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -693,12 +639,6 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -855,12 +795,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -873,12 +807,6 @@
           <t>Incendie / Foudre</t>
         </is>
       </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -891,12 +819,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -963,12 +885,6 @@
           <t>Facteur humain</t>
         </is>
       </c>
-      <c r="C34">
-        <v>4</v>
-      </c>
-      <c r="D34">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -981,12 +897,6 @@
           <t>Autres bestioles</t>
         </is>
       </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
-      <c r="D35">
-        <v>2.6</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -999,12 +909,6 @@
           <t>Criquets</t>
         </is>
       </c>
-      <c r="C36">
-        <v>3</v>
-      </c>
-      <c r="D36">
-        <v>2.6</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1017,12 +921,6 @@
           <t>Inondation</t>
         </is>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1197,12 +1095,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C47">
-        <v>3</v>
-      </c>
-      <c r="D47">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1214,12 +1106,6 @@
         <is>
           <t>Incendie / Foudre</t>
         </is>
-      </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
-      <c r="D48">
-        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/11/tbl_cata_type_marovoay_tous.xlsx
+++ b/docs/downloads/11/tbl_cata_type_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -937,13 +937,13 @@
         <v>272</v>
       </c>
       <c r="D38">
-        <v>52.4</v>
+        <v>190.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -955,13 +955,13 @@
         <v>104</v>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -973,13 +973,13 @@
         <v>42</v>
       </c>
       <c r="D40">
-        <v>8.1</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -991,13 +991,13 @@
         <v>42</v>
       </c>
       <c r="D41">
-        <v>8.1</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1009,13 +1009,13 @@
         <v>20</v>
       </c>
       <c r="D42">
-        <v>3.9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1027,13 +1027,13 @@
         <v>18</v>
       </c>
       <c r="D43">
-        <v>3.5</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1045,13 +1045,13 @@
         <v>16</v>
       </c>
       <c r="D44">
-        <v>3.1</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1063,13 +1063,13 @@
         <v>16</v>
       </c>
       <c r="D45">
-        <v>3.1</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1081,13 +1081,13 @@
         <v>15</v>
       </c>
       <c r="D46">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
